--- a/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0001T0006Z000C1N18_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0001T0006Z000C1N18_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>52.29833994879525</v>
+        <v>8.498480241679228</v>
       </c>
       <c r="D2" t="n">
-        <v>52.26368998027649</v>
+        <v>8.49284962179493</v>
       </c>
       <c r="E2" t="n">
-        <v>13.05725371217615</v>
+        <v>2.121803728228625</v>
       </c>
       <c r="F2" t="n">
-        <v>13.00150964143348</v>
+        <v>2.11274531673294</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.20941524398147</v>
+        <v>6.69652997714699</v>
       </c>
       <c r="D3" t="n">
-        <v>41.73117514121005</v>
+        <v>6.781315960446634</v>
       </c>
       <c r="E3" t="n">
-        <v>13.05725371217615</v>
+        <v>2.121803728228625</v>
       </c>
       <c r="F3" t="n">
-        <v>13.00150964143348</v>
+        <v>2.11274531673294</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>45.34184747165806</v>
+        <v>7.368050214144436</v>
       </c>
       <c r="D4" t="n">
-        <v>45.2642456416177</v>
+        <v>7.355439916762876</v>
       </c>
       <c r="E4" t="n">
-        <v>13.05725371217615</v>
+        <v>2.121803728228625</v>
       </c>
       <c r="F4" t="n">
-        <v>13.00150964143348</v>
+        <v>2.11274531673294</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>46.71280951544118</v>
+        <v>7.590831546259192</v>
       </c>
       <c r="D5" t="n">
-        <v>46.77292003032402</v>
+        <v>7.600599504927652</v>
       </c>
       <c r="E5" t="n">
-        <v>13.05725371217615</v>
+        <v>2.121803728228625</v>
       </c>
       <c r="F5" t="n">
-        <v>13.00150964143348</v>
+        <v>2.11274531673294</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>18.17745747749813</v>
+        <v>2.953836840093446</v>
       </c>
       <c r="D6" t="n">
-        <v>18.72165339915195</v>
+        <v>3.042268677362192</v>
       </c>
       <c r="E6" t="n">
-        <v>13.05725371217615</v>
+        <v>2.121803728228625</v>
       </c>
       <c r="F6" t="n">
-        <v>13.00150964143348</v>
+        <v>2.11274531673294</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>10.55218567392428</v>
+        <v>1.714730172012695</v>
       </c>
       <c r="D7" t="n">
-        <v>10.27915264041957</v>
+        <v>1.670362304068181</v>
       </c>
       <c r="E7" t="n">
-        <v>13.05725371217615</v>
+        <v>2.121803728228625</v>
       </c>
       <c r="F7" t="n">
-        <v>13.00150964143348</v>
+        <v>2.11274531673294</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>18.31961458793502</v>
+        <v>2.976937370539442</v>
       </c>
       <c r="D8" t="n">
-        <v>18.74375213633309</v>
+        <v>3.045859722154127</v>
       </c>
       <c r="E8" t="n">
-        <v>13.05725371217615</v>
+        <v>2.121803728228625</v>
       </c>
       <c r="F8" t="n">
-        <v>13.00150964143348</v>
+        <v>2.11274531673294</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>27.85972704770979</v>
+        <v>4.527205645252841</v>
       </c>
       <c r="D9" t="n">
-        <v>27.8831741110897</v>
+        <v>4.531015793052076</v>
       </c>
       <c r="E9" t="n">
-        <v>13.05725371217615</v>
+        <v>2.121803728228625</v>
       </c>
       <c r="F9" t="n">
-        <v>13.00150964143348</v>
+        <v>2.11274531673294</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>9.668911044158381</v>
+        <v>1.571198044675737</v>
       </c>
       <c r="D10" t="n">
-        <v>9.70982511347912</v>
+        <v>1.577846580940357</v>
       </c>
       <c r="E10" t="n">
-        <v>13.05725371217615</v>
+        <v>2.121803728228625</v>
       </c>
       <c r="F10" t="n">
-        <v>13.00150964143348</v>
+        <v>2.11274531673294</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>29.91587093431536</v>
+        <v>4.861329026826247</v>
       </c>
       <c r="D11" t="n">
-        <v>30.28875316568904</v>
+        <v>4.921922389424469</v>
       </c>
       <c r="E11" t="n">
-        <v>13.05725371217615</v>
+        <v>2.121803728228625</v>
       </c>
       <c r="F11" t="n">
-        <v>13.00150964143348</v>
+        <v>2.11274531673294</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>25.01324631618585</v>
+        <v>4.0646525263802</v>
       </c>
       <c r="D12" t="n">
-        <v>24.82364462249863</v>
+        <v>4.033842251156028</v>
       </c>
       <c r="E12" t="n">
-        <v>13.05725371217615</v>
+        <v>2.121803728228625</v>
       </c>
       <c r="F12" t="n">
-        <v>13.00150964143348</v>
+        <v>2.11274531673294</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>37.52107546578062</v>
+        <v>6.097174763189351</v>
       </c>
       <c r="D13" t="n">
-        <v>37.03519391237567</v>
+        <v>6.018219010761046</v>
       </c>
       <c r="E13" t="n">
-        <v>13.05725371217615</v>
+        <v>2.121803728228625</v>
       </c>
       <c r="F13" t="n">
-        <v>13.00150964143348</v>
+        <v>2.11274531673294</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>30.57402228187673</v>
+        <v>4.968278620804968</v>
       </c>
       <c r="D14" t="n">
-        <v>30.31306705085503</v>
+        <v>4.925873395763943</v>
       </c>
       <c r="E14" t="n">
-        <v>13.05725371217615</v>
+        <v>2.121803728228625</v>
       </c>
       <c r="F14" t="n">
-        <v>13.00150964143348</v>
+        <v>2.11274531673294</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>30.83845594346282</v>
+        <v>5.011249090812708</v>
       </c>
       <c r="D15" t="n">
-        <v>30.73207284924102</v>
+        <v>4.993961838001667</v>
       </c>
       <c r="E15" t="n">
-        <v>13.05725371217615</v>
+        <v>2.121803728228625</v>
       </c>
       <c r="F15" t="n">
-        <v>13.00150964143348</v>
+        <v>2.11274531673294</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>41.77610379303685</v>
+        <v>6.788616866368489</v>
       </c>
       <c r="D16" t="n">
-        <v>41.52661792998233</v>
+        <v>6.748075413622129</v>
       </c>
       <c r="E16" t="n">
-        <v>13.05725371217615</v>
+        <v>2.121803728228625</v>
       </c>
       <c r="F16" t="n">
-        <v>13.00150964143348</v>
+        <v>2.11274531673294</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>40.51259332525169</v>
+        <v>6.583296415353399</v>
       </c>
       <c r="D17" t="n">
-        <v>40.39775868284536</v>
+        <v>6.564635785962372</v>
       </c>
       <c r="E17" t="n">
-        <v>13.05725371217615</v>
+        <v>2.121803728228625</v>
       </c>
       <c r="F17" t="n">
-        <v>13.00150964143348</v>
+        <v>2.11274531673294</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>42.03117296092307</v>
+        <v>6.830065606149998</v>
       </c>
       <c r="D18" t="n">
-        <v>42.16610802290802</v>
+        <v>6.851992553722553</v>
       </c>
       <c r="E18" t="n">
-        <v>13.05725371217615</v>
+        <v>2.121803728228625</v>
       </c>
       <c r="F18" t="n">
-        <v>13.00150964143348</v>
+        <v>2.11274531673294</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>54.53658622955241</v>
+        <v>8.862195262302267</v>
       </c>
       <c r="D19" t="n">
-        <v>54.29474277949623</v>
+        <v>8.822895701668138</v>
       </c>
       <c r="E19" t="n">
-        <v>13.05725371217615</v>
+        <v>2.121803728228625</v>
       </c>
       <c r="F19" t="n">
-        <v>13.00150964143348</v>
+        <v>2.11274531673294</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
